--- a/Result/profitability/8085.xlsx
+++ b/Result/profitability/8085.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.25125</v>
+        <v>-0.23625</v>
       </c>
       <c r="N2" t="n">
-        <v>5.64</v>
+        <v>5.438750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15625</v>
+        <v>-0.16875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.06625</v>
+        <v>5.13</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10625</v>
+        <v>-0.11125</v>
       </c>
       <c r="N4" t="n">
-        <v>4.765000000000001</v>
+        <v>4.48625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.17125</v>
+        <v>-0.155</v>
       </c>
       <c r="N5" t="n">
-        <v>3.565</v>
+        <v>3.345</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.17125</v>
+        <v>-0.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.63</v>
+        <v>2.60375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.32125</v>
+        <v>-0.2825</v>
       </c>
       <c r="N7" t="n">
-        <v>1.70625</v>
+        <v>1.52625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.28125</v>
+        <v>-0.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.47125</v>
+        <v>1.665</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8085</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>145</v>
+      </c>
+      <c r="D75" t="n">
+        <v>137</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-20.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.93875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4144385026737967</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2954545454545454</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.249645390070922</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
